--- a/Acumulado_mensual_ant.xlsx
+++ b/Acumulado_mensual_ant.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>multi-venue - Sales Summary - 2025-07-01/2025-07-16</t>
+          <t>multi-venue - Sales Summary - 2025-07-01/2025-07-19</t>
         </is>
       </c>
     </row>
@@ -462,10 +462,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>48581.69</v>
+        <v>59306.62</v>
       </c>
       <c r="C3" t="n">
-        <v>48581.69</v>
+        <v>59306.62</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -474,7 +474,7 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>3966</v>
       </c>
     </row>
     <row r="4">
@@ -484,10 +484,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>44694.46</v>
+        <v>53578.42</v>
       </c>
       <c r="C4" t="n">
-        <v>44694.46</v>
+        <v>53578.42</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -496,7 +496,7 @@
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>3297</v>
       </c>
     </row>
     <row r="5">
@@ -506,10 +506,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>54929.35</v>
+        <v>67714.39</v>
       </c>
       <c r="C5" t="n">
-        <v>54929.35</v>
+        <v>67714.39</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -518,7 +518,7 @@
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>4558</v>
       </c>
     </row>
     <row r="6">
@@ -528,10 +528,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>35695.81</v>
+        <v>43861.28</v>
       </c>
       <c r="C6" t="n">
-        <v>35695.81</v>
+        <v>43861.28</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -540,7 +540,7 @@
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>2665</v>
       </c>
     </row>
     <row r="7">
@@ -550,10 +550,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>12418.71</v>
+        <v>14190.74</v>
       </c>
       <c r="C7" t="n">
-        <v>12418.71</v>
+        <v>14190.74</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -562,7 +562,7 @@
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>1157</v>
       </c>
     </row>
     <row r="8">
@@ -572,10 +572,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>15888.8</v>
+        <v>19679.78</v>
       </c>
       <c r="C8" t="n">
-        <v>15888.8</v>
+        <v>19679.78</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -584,7 +584,7 @@
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>1111</v>
       </c>
     </row>
     <row r="9">
@@ -594,10 +594,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>212208.82</v>
+        <v>258331.23</v>
       </c>
       <c r="C9" t="n">
-        <v>212208.82</v>
+        <v>258331.23</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>

--- a/Acumulado_mensual_ant.xlsx
+++ b/Acumulado_mensual_ant.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>multi-venue - Sales Summary - 2025-07-01/2025-07-19</t>
+          <t>multi-venue - Sales Summary - 2025-07-01/2025-07-26</t>
         </is>
       </c>
     </row>
@@ -462,10 +462,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>59306.62</v>
+        <v>83655.07000000001</v>
       </c>
       <c r="C3" t="n">
-        <v>59306.62</v>
+        <v>83655.07000000001</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -474,7 +474,7 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>3966</v>
+        <v>5524</v>
       </c>
     </row>
     <row r="4">
@@ -484,10 +484,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>53578.42</v>
+        <v>72297.95</v>
       </c>
       <c r="C4" t="n">
-        <v>53578.42</v>
+        <v>72297.95</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -496,7 +496,7 @@
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>3297</v>
+        <v>4506</v>
       </c>
     </row>
     <row r="5">
@@ -506,10 +506,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>67714.39</v>
+        <v>97878.12</v>
       </c>
       <c r="C5" t="n">
-        <v>67714.39</v>
+        <v>97878.12</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -518,7 +518,7 @@
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>4558</v>
+        <v>6453</v>
       </c>
     </row>
     <row r="6">
@@ -528,10 +528,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>43861.28</v>
+        <v>59578.76</v>
       </c>
       <c r="C6" t="n">
-        <v>43861.28</v>
+        <v>59578.76</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -540,7 +540,7 @@
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>2665</v>
+        <v>3669</v>
       </c>
     </row>
     <row r="7">
@@ -550,10 +550,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>14190.74</v>
+        <v>19447.81</v>
       </c>
       <c r="C7" t="n">
-        <v>14190.74</v>
+        <v>19447.81</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -562,7 +562,7 @@
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>1157</v>
+        <v>1607</v>
       </c>
     </row>
     <row r="8">
@@ -572,10 +572,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>19679.78</v>
+        <v>28028.28</v>
       </c>
       <c r="C8" t="n">
-        <v>19679.78</v>
+        <v>28028.28</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -584,7 +584,7 @@
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>1111</v>
+        <v>1604</v>
       </c>
     </row>
     <row r="9">
@@ -594,10 +594,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>258331.23</v>
+        <v>360885.99</v>
       </c>
       <c r="C9" t="n">
-        <v>258331.23</v>
+        <v>360885.99</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>

--- a/Acumulado_mensual_ant.xlsx
+++ b/Acumulado_mensual_ant.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>multi-venue - Sales Summary - 2025-07-01/2025-07-26</t>
+          <t>multi-venue - Sales Summary - 2025-08-01/2025-08-02</t>
         </is>
       </c>
     </row>
@@ -462,10 +462,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>83655.07000000001</v>
+        <v>8511.02</v>
       </c>
       <c r="C3" t="n">
-        <v>83655.07000000001</v>
+        <v>8511.02</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -474,7 +474,7 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>5524</v>
+        <v>552</v>
       </c>
     </row>
     <row r="4">
@@ -484,10 +484,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>72297.95</v>
+        <v>7105.8</v>
       </c>
       <c r="C4" t="n">
-        <v>72297.95</v>
+        <v>7105.8</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -496,7 +496,7 @@
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>4506</v>
+        <v>454</v>
       </c>
     </row>
     <row r="5">
@@ -506,10 +506,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>97878.12</v>
+        <v>9634.440000000001</v>
       </c>
       <c r="C5" t="n">
-        <v>97878.12</v>
+        <v>9634.440000000001</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -518,7 +518,7 @@
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>6453</v>
+        <v>619</v>
       </c>
     </row>
     <row r="6">
@@ -528,10 +528,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>59578.76</v>
+        <v>6435.61</v>
       </c>
       <c r="C6" t="n">
-        <v>59578.76</v>
+        <v>6435.61</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -540,7 +540,7 @@
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>3669</v>
+        <v>390</v>
       </c>
     </row>
     <row r="7">
@@ -550,10 +550,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>19447.81</v>
+        <v>1849.92</v>
       </c>
       <c r="C7" t="n">
-        <v>19447.81</v>
+        <v>1849.92</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -562,7 +562,7 @@
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>1607</v>
+        <v>172</v>
       </c>
     </row>
     <row r="8">
@@ -572,10 +572,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>28028.28</v>
+        <v>3043.24</v>
       </c>
       <c r="C8" t="n">
-        <v>28028.28</v>
+        <v>3043.24</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -584,7 +584,7 @@
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>1604</v>
+        <v>159</v>
       </c>
     </row>
     <row r="9">
@@ -594,10 +594,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>360885.99</v>
+        <v>36580.03</v>
       </c>
       <c r="C9" t="n">
-        <v>360885.99</v>
+        <v>36580.03</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>

--- a/Acumulado_mensual_ant.xlsx
+++ b/Acumulado_mensual_ant.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>multi-venue - Sales Summary - 2025-08-01/2025-08-02</t>
+          <t>multi-venue - Sales Summary - 2025-08-01/2025-08-09</t>
         </is>
       </c>
     </row>
@@ -462,10 +462,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>8511.02</v>
+        <v>33420.18</v>
       </c>
       <c r="C3" t="n">
-        <v>8511.02</v>
+        <v>33420.18</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -474,7 +474,7 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>552</v>
+        <v>2182</v>
       </c>
     </row>
     <row r="4">
@@ -484,10 +484,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7105.8</v>
+        <v>24065.19</v>
       </c>
       <c r="C4" t="n">
-        <v>7105.8</v>
+        <v>24065.19</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -496,7 +496,7 @@
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>454</v>
+        <v>1540</v>
       </c>
     </row>
     <row r="5">
@@ -506,10 +506,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>9634.440000000001</v>
+        <v>38518.61</v>
       </c>
       <c r="C5" t="n">
-        <v>9634.440000000001</v>
+        <v>38518.61</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -518,7 +518,7 @@
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>619</v>
+        <v>2454</v>
       </c>
     </row>
     <row r="6">
@@ -528,10 +528,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6435.61</v>
+        <v>23502.98</v>
       </c>
       <c r="C6" t="n">
-        <v>6435.61</v>
+        <v>23502.98</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -540,7 +540,7 @@
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>390</v>
+        <v>1375</v>
       </c>
     </row>
     <row r="7">
@@ -550,10 +550,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1849.92</v>
+        <v>7069.92</v>
       </c>
       <c r="C7" t="n">
-        <v>1849.92</v>
+        <v>7069.92</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -562,7 +562,7 @@
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>172</v>
+        <v>624</v>
       </c>
     </row>
     <row r="8">
@@ -572,10 +572,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3043.24</v>
+        <v>11269.05</v>
       </c>
       <c r="C8" t="n">
-        <v>3043.24</v>
+        <v>11269.05</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -584,7 +584,7 @@
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>159</v>
+        <v>617</v>
       </c>
     </row>
     <row r="9">
@@ -594,10 +594,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>36580.03</v>
+        <v>137845.93</v>
       </c>
       <c r="C9" t="n">
-        <v>36580.03</v>
+        <v>137845.93</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>

--- a/Acumulado_mensual_ant.xlsx
+++ b/Acumulado_mensual_ant.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>multi-venue - Sales Summary - 2025-08-01/2025-08-09</t>
+          <t>multi-venue - Sales Summary - 2025-08-01/2025-08-16</t>
         </is>
       </c>
     </row>
@@ -462,10 +462,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>33420.18</v>
+        <v>53092.65</v>
       </c>
       <c r="C3" t="n">
-        <v>33420.18</v>
+        <v>53092.65</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -474,7 +474,7 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>2182</v>
+        <v>3533</v>
       </c>
     </row>
     <row r="4">
@@ -484,10 +484,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>24065.19</v>
+        <v>42680.8</v>
       </c>
       <c r="C4" t="n">
-        <v>24065.19</v>
+        <v>42680.8</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -496,7 +496,7 @@
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>1540</v>
+        <v>2724</v>
       </c>
     </row>
     <row r="5">
@@ -506,10 +506,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>38518.61</v>
+        <v>63069.32</v>
       </c>
       <c r="C5" t="n">
-        <v>38518.61</v>
+        <v>63069.32</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -518,7 +518,7 @@
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>2454</v>
+        <v>4088</v>
       </c>
     </row>
     <row r="6">
@@ -528,10 +528,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>23502.98</v>
+        <v>41642.22</v>
       </c>
       <c r="C6" t="n">
-        <v>23502.98</v>
+        <v>41642.22</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -540,7 +540,7 @@
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>1375</v>
+        <v>2360</v>
       </c>
     </row>
     <row r="7">
@@ -550,10 +550,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>7069.92</v>
+        <v>12407.28</v>
       </c>
       <c r="C7" t="n">
-        <v>7069.92</v>
+        <v>12407.28</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -562,7 +562,7 @@
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>624</v>
+        <v>1084</v>
       </c>
     </row>
     <row r="8">
@@ -572,10 +572,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>11269.05</v>
+        <v>18668.25</v>
       </c>
       <c r="C8" t="n">
-        <v>11269.05</v>
+        <v>18668.25</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -584,7 +584,7 @@
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>617</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="9">
@@ -594,10 +594,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>137845.93</v>
+        <v>231560.52</v>
       </c>
       <c r="C9" t="n">
-        <v>137845.93</v>
+        <v>231560.52</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>

--- a/Acumulado_mensual_ant.xlsx
+++ b/Acumulado_mensual_ant.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>multi-venue - Sales Summary - 2025-08-01/2025-08-16</t>
+          <t>multi-venue - Sales Summary - 2025-08-01/2025-08-23</t>
         </is>
       </c>
     </row>
@@ -462,10 +462,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>53092.65</v>
+        <v>71849.71000000001</v>
       </c>
       <c r="C3" t="n">
-        <v>53092.65</v>
+        <v>71849.71000000001</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -474,7 +474,7 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>3533</v>
+        <v>4829</v>
       </c>
     </row>
     <row r="4">
@@ -484,10 +484,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>42680.8</v>
+        <v>61901.25</v>
       </c>
       <c r="C4" t="n">
-        <v>42680.8</v>
+        <v>61901.25</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -496,7 +496,7 @@
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>2724</v>
+        <v>3923</v>
       </c>
     </row>
     <row r="5">
@@ -506,10 +506,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>63069.32</v>
+        <v>85668.53999999999</v>
       </c>
       <c r="C5" t="n">
-        <v>63069.32</v>
+        <v>85668.53999999999</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -518,7 +518,7 @@
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>4088</v>
+        <v>5644</v>
       </c>
     </row>
     <row r="6">
@@ -528,10 +528,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>41642.22</v>
+        <v>53619.96</v>
       </c>
       <c r="C6" t="n">
-        <v>41642.22</v>
+        <v>53619.96</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -540,7 +540,7 @@
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>2360</v>
+        <v>3133</v>
       </c>
     </row>
     <row r="7">
@@ -550,10 +550,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>12407.28</v>
+        <v>16825.16</v>
       </c>
       <c r="C7" t="n">
-        <v>12407.28</v>
+        <v>16825.16</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -562,7 +562,7 @@
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>1084</v>
+        <v>1482</v>
       </c>
     </row>
     <row r="8">
@@ -572,10 +572,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>18668.25</v>
+        <v>25373.01</v>
       </c>
       <c r="C8" t="n">
-        <v>18668.25</v>
+        <v>25373.01</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -584,7 +584,7 @@
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>1040</v>
+        <v>1428</v>
       </c>
     </row>
     <row r="9">
@@ -594,10 +594,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>231560.52</v>
+        <v>315237.63</v>
       </c>
       <c r="C9" t="n">
-        <v>231560.52</v>
+        <v>315237.63</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>

--- a/Acumulado_mensual_ant.xlsx
+++ b/Acumulado_mensual_ant.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>multi-venue - Sales Summary - 2025-08-01/2025-08-23</t>
+          <t>multi-venue - Sales Summary - 2025-08-01/2025-08-30</t>
         </is>
       </c>
     </row>
@@ -462,10 +462,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>71849.71000000001</v>
+        <v>88270.08</v>
       </c>
       <c r="C3" t="n">
-        <v>71849.71000000001</v>
+        <v>88270.08</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -474,7 +474,7 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>4829</v>
+        <v>5991</v>
       </c>
     </row>
     <row r="4">
@@ -484,10 +484,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>61901.25</v>
+        <v>79527.33</v>
       </c>
       <c r="C4" t="n">
-        <v>61901.25</v>
+        <v>79527.33</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -496,7 +496,7 @@
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>3923</v>
+        <v>5045</v>
       </c>
     </row>
     <row r="5">
@@ -506,10 +506,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>85668.53999999999</v>
+        <v>107381.05</v>
       </c>
       <c r="C5" t="n">
-        <v>85668.53999999999</v>
+        <v>107381.05</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -518,7 +518,7 @@
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>5644</v>
+        <v>7113</v>
       </c>
     </row>
     <row r="6">
@@ -528,10 +528,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>53619.96</v>
+        <v>65236.44</v>
       </c>
       <c r="C6" t="n">
-        <v>53619.96</v>
+        <v>65236.44</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -540,7 +540,7 @@
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>3133</v>
+        <v>3894</v>
       </c>
     </row>
     <row r="7">
@@ -550,10 +550,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>16825.16</v>
+        <v>21710.62</v>
       </c>
       <c r="C7" t="n">
-        <v>16825.16</v>
+        <v>21710.62</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -562,7 +562,7 @@
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>1482</v>
+        <v>1897</v>
       </c>
     </row>
     <row r="8">
@@ -572,10 +572,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>25373.01</v>
+        <v>30946.33</v>
       </c>
       <c r="C8" t="n">
-        <v>25373.01</v>
+        <v>30946.33</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -584,7 +584,7 @@
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>1428</v>
+        <v>1770</v>
       </c>
     </row>
     <row r="9">
@@ -594,10 +594,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>315237.63</v>
+        <v>393071.85</v>
       </c>
       <c r="C9" t="n">
-        <v>315237.63</v>
+        <v>393071.85</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>

--- a/Acumulado_mensual_ant.xlsx
+++ b/Acumulado_mensual_ant.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>multi-venue - Sales Summary - 2025-08-01/2025-08-30</t>
+          <t>multi-venue - Sales Summary - 2025-09-01/2025-09-06</t>
         </is>
       </c>
     </row>
@@ -462,10 +462,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>88270.08</v>
+        <v>13876.94</v>
       </c>
       <c r="C3" t="n">
-        <v>88270.08</v>
+        <v>13876.94</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -474,7 +474,7 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>5991</v>
+        <v>975</v>
       </c>
     </row>
     <row r="4">
@@ -484,10 +484,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>79527.33</v>
+        <v>12027.33</v>
       </c>
       <c r="C4" t="n">
-        <v>79527.33</v>
+        <v>12027.33</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -496,7 +496,7 @@
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>5045</v>
+        <v>769</v>
       </c>
     </row>
     <row r="5">
@@ -506,10 +506,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>107381.05</v>
+        <v>16265.81</v>
       </c>
       <c r="C5" t="n">
-        <v>107381.05</v>
+        <v>16265.81</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -518,7 +518,7 @@
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>7113</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="6">
@@ -528,10 +528,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>65236.44</v>
+        <v>10872.97</v>
       </c>
       <c r="C6" t="n">
-        <v>65236.44</v>
+        <v>10872.97</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -540,7 +540,7 @@
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>3894</v>
+        <v>697</v>
       </c>
     </row>
     <row r="7">
@@ -550,10 +550,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>21710.62</v>
+        <v>3548.46</v>
       </c>
       <c r="C7" t="n">
-        <v>21710.62</v>
+        <v>3548.46</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -562,7 +562,7 @@
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>1897</v>
+        <v>299</v>
       </c>
     </row>
     <row r="8">
@@ -572,10 +572,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>30946.33</v>
+        <v>4726.07</v>
       </c>
       <c r="C8" t="n">
-        <v>30946.33</v>
+        <v>4726.07</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -584,7 +584,7 @@
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>1770</v>
+        <v>303</v>
       </c>
     </row>
     <row r="9">
@@ -594,10 +594,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>393071.85</v>
+        <v>61317.58</v>
       </c>
       <c r="C9" t="n">
-        <v>393071.85</v>
+        <v>61317.58</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
